--- a/examples/demos/00_START_HERE.xlsx
+++ b/examples/demos/00_START_HERE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BD7392-8D56-4481-B7B6-DE6366978812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA812C-F034-4EDF-AB33-62C8D7722A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>ModelRisk MCP — Demo Gallery</t>
   </si>
@@ -142,34 +142,31 @@
     <t>HOW TO USE</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Pick a demo from the table above that matches the problem you care about.</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>In Claude, say:  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/&lt;file&gt; in Excel  — then read that workbook's README sheet.</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Follow the README steps in order, typing each PROMPT to Claude. Each demo is self-contained and takes about 5-10 minutes.</t>
-  </si>
-  <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>Note: any demo that runs a simulation needs a licensed copy of ModelRisk.</t>
+    <t>Save this gallery folder anywhere on your PC.</t>
+  </si>
+  <si>
+    <t>Once per session, tell Claude where it is:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 01_build_model_from_brief.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Every demo README has a FAST TRACK — one prompt that runs the whole demo — and numbered steps if you want to learn one capability at a time.</t>
+  </si>
+  <si>
+    <t>Demos are independent; each takes 5-10 minutes.</t>
+  </si>
+  <si>
+    <t>YOU NEED</t>
+  </si>
+  <si>
+    <t>Excel on Windows with a licensed ModelRisk add-in.</t>
+  </si>
+  <si>
+    <t>modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Note: any demo that runs a simulation needs the ModelRisk add-in live.</t>
   </si>
   <si>
     <t>COLOUR LEGEND</t>
@@ -229,6 +226,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
@@ -237,12 +240,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -296,32 +293,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,7 +625,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -636,25 +634,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
     </row>
     <row r="4" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
@@ -667,7 +665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -678,7 +676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -689,7 +687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -700,7 +698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -711,7 +709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -722,7 +720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -733,7 +731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -744,7 +742,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -755,7 +753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
@@ -766,7 +764,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -777,7 +775,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -789,95 +787,132 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="3">
+        <v>1</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="3">
+        <v>2</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="3">
+        <v>3</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="3" t="s">
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="3">
+        <v>4</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C23" s="11"/>
+    </row>
+    <row r="25" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="9" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B26" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-    </row>
-    <row r="24" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B27" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B25" s="2" t="s">
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B28" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B26" s="4" t="s">
+      <c r="C28" s="11"/>
+    </row>
+    <row r="30" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="9" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="5"/>
+      <c r="B31" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="5"/>
-      <c r="B29" s="2" t="s">
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="6"/>
+      <c r="B32" s="12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A30" s="6"/>
-      <c r="B30" s="2" t="s">
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A33" s="7"/>
+      <c r="B33" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A31" s="7"/>
-      <c r="B31" s="2" t="s">
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="4"/>
+      <c r="B34" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="8"/>
-      <c r="B32" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="C34" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A28:C28"/>
+  <mergeCells count="18">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>

--- a/examples/demos/00_START_HERE.xlsx
+++ b/examples/demos/00_START_HERE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA812C-F034-4EDF-AB33-62C8D7722A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD73B855-0AD2-45F9-82DC-469059D95F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,13 +306,13 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -644,15 +644,15 @@
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
     </row>
     <row r="4" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
@@ -787,116 +787,121 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>1</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="11"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>2</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="11"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="11"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>3</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="11"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>4</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="11"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="25" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="11"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="11"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="11"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="30" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="11"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="6"/>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="11"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A33" s="7"/>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="11"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="4"/>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="11"/>
+      <c r="C34" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
@@ -910,11 +915,6 @@
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/demos/00_START_HERE.xlsx
+++ b/examples/demos/00_START_HERE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD73B855-0AD2-45F9-82DC-469059D95F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0EBE83-5EBD-4CAE-96E9-D1AB18577EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>ModelRisk MCP — Demo Gallery</t>
   </si>
   <si>
-    <t>Eleven hands-on demos — open any workbook and follow its README sheet.</t>
+    <t>Fifteen hands-on demos — open any workbook and follow its README sheet.</t>
   </si>
   <si>
     <t>WHAT THIS GALLERY CONTAINS</t>
@@ -137,6 +137,42 @@
   </si>
   <si>
     <t>build_executive_report, build_drivers_report, generate_executive_summary</t>
+  </si>
+  <si>
+    <t>12_fit_time_series.xlsx</t>
+  </si>
+  <si>
+    <t>CFO revenue projection — dynamics fitted from history</t>
+  </si>
+  <si>
+    <t>fit_time_series, read_vmrs</t>
+  </si>
+  <si>
+    <t>13_compare_options.xlsx</t>
+  </si>
+  <si>
+    <t>Two suppliers, one contract — P(A beats B)</t>
+  </si>
+  <si>
+    <t>compare_distributions, compute_correlation_matrix</t>
+  </si>
+  <si>
+    <t>14_backtest_forecast.xlsx</t>
+  </si>
+  <si>
+    <t>Was last year's forecast honestly calibrated?</t>
+  </si>
+  <si>
+    <t>backtest_output</t>
+  </si>
+  <si>
+    <t>15_uncertainty_sources.xlsx</t>
+  </si>
+  <si>
+    <t>More data or more capital? Epistemic vs aleatory</t>
+  </si>
+  <si>
+    <t>decompose_uncertainty</t>
   </si>
   <si>
     <t>HOW TO USE</t>
@@ -310,15 +346,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +661,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -634,11 +670,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="15" t="s">
@@ -648,11 +684,11 @@
       <c r="C2" s="9"/>
     </row>
     <row r="4" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
@@ -786,135 +822,179 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="10" t="s">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
-        <v>1</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="3">
-        <v>2</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="C17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="12" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="3">
-        <v>3</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
+        <v>1</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="3">
+        <v>2</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="9"/>
+    </row>
+    <row r="26" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="3">
+        <v>3</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="3">
         <v>4</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="25" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B26" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B27" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C27" s="9"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="30" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
+    <row r="29" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="6"/>
       <c r="B32" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C32" s="9"/>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="4"/>
-      <c r="B34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="9"/>
+    <row r="34" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="5"/>
+      <c r="B35" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="9"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="6"/>
+      <c r="B36" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A37" s="7"/>
+      <c r="B37" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="9"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="4"/>
+      <c r="B38" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
